--- a/wiki/reports/daily/2026-10-08_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-08_일일보고.xlsx
@@ -613,7 +613,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-08 07:58   |   전일: 10월 7일   |   월평균 기준: 이전 작업일 4일 평균   |   10월 누적 작업일: 5일</t>
+          <t>생성: 2026-10-08 16:00   |   전일: 10월 7일   |   월평균 기준: 이전 작업일 4일 평균   |   10월 누적 작업일: 5일</t>
         </is>
       </c>
     </row>
@@ -675,25 +675,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>50</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-40</v>
+        <v>-15</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.8</v>
+        <v>-0.3</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>50.5</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-40.5</v>
+        <v>-15.5</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.801980198019802</v>
+        <v>-0.3069306930693069</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -704,29 +704,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1750</v>
+        <v>6084</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>9721</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-7971</v>
+        <v>-3637</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.819977368583479</v>
+        <v>-0.3741384631210781</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>12874</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-11124</v>
+        <v>-6790</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-0.8640671120086997</v>
+        <v>-0.5274196054062451</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:29:10</t>
+          <t>1:41:24</t>
         </is>
       </c>
     </row>
@@ -737,25 +737,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>49</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-44</v>
+        <v>-21</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.8979591836734694</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>40.5</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-35.5</v>
+        <v>-12.5</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.8765432098765432</v>
+        <v>-0.308641975308642</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>910</v>
+        <v>7337</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>14210</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-13300</v>
+        <v>-6873</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.9359605911330049</v>
+        <v>-0.4836734693877551</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>12384.8</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-11474.75</v>
+        <v>-5047.75</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-0.9265225377985022</v>
+        <v>-0.4075778679424292</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:15:10</t>
+          <t>2:02:17</t>
         </is>
       </c>
     </row>
@@ -799,25 +799,25 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>99</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-84</v>
+        <v>-36</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.8484848484848485</v>
+        <v>-0.3636363636363636</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>91</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-76</v>
+        <v>-28</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.8351648351648352</v>
+        <v>-0.3076923076923077</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
@@ -828,29 +828,29 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>2660</v>
+        <v>13421</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>23931</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-21271</v>
+        <v>-10510</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.8888471020851615</v>
+        <v>-0.4391793071747942</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>25258.8</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-22598.75</v>
+        <v>-11837.75</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.8946899589251249</v>
+        <v>-0.4686593754639481</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>0:44:20</t>
+          <t>3:43:41</t>
         </is>
       </c>
     </row>
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>99</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-84</v>
+        <v>-36</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.8484848484848485</v>
+        <v>-0.3636363636363636</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>91</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-76</v>
+        <v>-28</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-0.8351648351648352</v>
+        <v>-0.3076923076923077</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
@@ -891,13 +891,13 @@
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="14" t="n">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>103695</v>
+        <v>114456</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1040,175 +1040,708 @@
         <v>10</v>
       </c>
       <c r="J4" s="19" t="n">
-        <v>1750</v>
+        <v>1700</v>
       </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
-          <t>0:29:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+          <t>0:28:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>0153 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>1020</v>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>0:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>130</v>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>0:02:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>110</v>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>0:01:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr"/>
+      <c r="I8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>110</v>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>0:01:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>0059</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr"/>
+      <c r="I9" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>2120</v>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>0:35:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr"/>
+      <c r="I10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>167</v>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>0:02:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>0149</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr"/>
+      <c r="I11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>501</v>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>0:08:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>225</v>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>0:03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>0:00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="14" t="n">
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>6084</v>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>1:41:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>■ GX7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>형상</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>날수(F)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>날경(Ø)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>상크경(Ø)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>코팅</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>수량(개)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>시간합계(초)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>시간(H:M:S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="14" t="n">
-        <v>1750</v>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>0:29:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>■ GX7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>형상</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>날수(F)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>날경(Ø)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>상크경(Ø)</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>코팅</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>특이사항</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>수량(개)</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t>시간합계(초)</t>
-        </is>
-      </c>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t>시간(H:M:S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>평</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="n">
+      <c r="E18" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>0160</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr"/>
+      <c r="I18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>910</v>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>0:15:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D19" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E19" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr"/>
+      <c r="I19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="24" t="n">
+        <v>546</v>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>0:09:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>R0.3_라핑</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>0160</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr"/>
-      <c r="I9" s="24" t="n">
+      <c r="H20" s="22" t="inlineStr"/>
+      <c r="I20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>590</v>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>0:09:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>0160 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr"/>
+      <c r="I21" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="24" t="n">
+        <v>990</v>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>0:16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J9" s="24" t="n">
-        <v>910</v>
-      </c>
-      <c r="K9" s="22" t="inlineStr">
-        <is>
-          <t>0:15:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>0149</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr"/>
+      <c r="I22" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="J22" s="24" t="n">
+        <v>4301</v>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>1:11:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>910</v>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>0:15:10</t>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>7337</v>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>2:02:17</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A10:H10"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/wiki/reports/daily/2026-10-08_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-08_일일보고.xlsx
@@ -613,7 +613,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-08 16:00   |   전일: 10월 7일   |   월평균 기준: 이전 작업일 4일 평균   |   10월 누적 작업일: 5일</t>
+          <t>생성: 2026-10-08 16:53   |   전일: 10월 7일   |   월평균 기준: 이전 작업일 4일 평균   |   10월 누적 작업일: 5일</t>
         </is>
       </c>
     </row>
@@ -675,25 +675,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>50</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.3</v>
+        <v>-0.16</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>50.5</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-15.5</v>
+        <v>-8.5</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.3069306930693069</v>
+        <v>-0.1683168316831683</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -704,29 +704,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>6084</v>
+        <v>8014</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>9721</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-3637</v>
+        <v>-1707</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.3741384631210781</v>
+        <v>-0.1755992181874293</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>12874</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-6790</v>
+        <v>-4860</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-0.5274196054062451</v>
+        <v>-0.3775050489358397</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>1:41:24</t>
+          <t>2:13:34</t>
         </is>
       </c>
     </row>
@@ -737,25 +737,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>49</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-21</v>
+        <v>-14</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>40.5</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-12.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.308641975308642</v>
+        <v>-0.1358024691358025</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7337</v>
+        <v>9035</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>14210</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-6873</v>
+        <v>-5175</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.4836734693877551</v>
+        <v>-0.3641801548205489</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>12384.8</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-5047.75</v>
+        <v>-3349.75</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-0.4075778679424292</v>
+        <v>-0.2704737681422718</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>2:02:17</t>
+          <t>2:30:35</t>
         </is>
       </c>
     </row>
@@ -799,25 +799,25 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>99</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-36</v>
+        <v>-22</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.3636363636363636</v>
+        <v>-0.2222222222222222</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>91</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.3076923076923077</v>
+        <v>-0.1538461538461539</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
@@ -828,29 +828,29 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>13421</v>
+        <v>17049</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>23931</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-10510</v>
+        <v>-6882</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.4391793071747942</v>
+        <v>-0.287576783251849</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>25258.8</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-11837.75</v>
+        <v>-8209.75</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.4686593754639481</v>
+        <v>-0.3250259810956599</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>3:43:41</t>
+          <t>4:44:09</t>
         </is>
       </c>
     </row>
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>99</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-36</v>
+        <v>-22</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.3636363636363636</v>
+        <v>-0.2222222222222222</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>91</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-0.3076923076923077</v>
+        <v>-0.1538461538461539</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
@@ -891,13 +891,13 @@
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="14" t="n">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>114456</v>
+        <v>118084</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1035,7 +1035,11 @@
           <t>0153</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr"/>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" s="19" t="n">
         <v>10</v>
       </c>
@@ -1076,7 +1080,11 @@
           <t>0153 ㅋㅌ</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr"/>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" s="19" t="n">
         <v>6</v>
       </c>
@@ -1117,7 +1125,11 @@
           <t>0104</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr"/>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I6" s="19" t="n">
         <v>1</v>
       </c>
@@ -1158,7 +1170,11 @@
           <t>0104</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" s="19" t="n">
         <v>1</v>
       </c>
@@ -1199,7 +1215,11 @@
           <t>0104</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr"/>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I8" s="19" t="n">
         <v>1</v>
       </c>
@@ -1240,7 +1260,11 @@
           <t>0059</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr"/>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I9" s="19" t="n">
         <v>10</v>
       </c>
@@ -1281,7 +1305,11 @@
           <t>0120</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr"/>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I10" s="19" t="n">
         <v>1</v>
       </c>
@@ -1322,7 +1350,11 @@
           <t>0149</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr"/>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I11" s="19" t="n">
         <v>3</v>
       </c>
@@ -1360,19 +1392,23 @@
       </c>
       <c r="G12" s="18" t="inlineStr">
         <is>
-          <t>0153</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr"/>
+          <t>0153, 0124</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" s="19" t="n">
-        <v>225</v>
+        <v>675</v>
       </c>
       <c r="K12" s="17" t="inlineStr">
         <is>
-          <t>0:03:45</t>
+          <t>0:11:15</t>
         </is>
       </c>
     </row>
@@ -1404,197 +1440,209 @@
           <t>0153</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr"/>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" s="19" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="K13" s="17" t="inlineStr">
         <is>
-          <t>0:00:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+          <t>0:03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>0124</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>636</v>
+      </c>
+      <c r="K14" s="17" t="inlineStr">
+        <is>
+          <t>0:10:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>620</v>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>0:10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="14" t="n">
-        <v>35</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>6084</v>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
-        <is>
-          <t>1:41:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>8014</v>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>2:13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K17" s="21" t="inlineStr">
+      <c r="K19" s="21" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>평</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>뮤</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="inlineStr">
-        <is>
-          <t>0160</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr"/>
-      <c r="I18" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>910</v>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
-        <is>
-          <t>0:15:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>R0.5</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>뮤</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>0153</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr"/>
-      <c r="I19" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>546</v>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
-        <is>
-          <t>0:09:06</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>R0.3_라핑</t>
+          <t>평</t>
         </is>
       </c>
       <c r="C20" s="22" t="n">
@@ -1616,30 +1664,34 @@
           <t>0160</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr"/>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" s="24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>590</v>
+        <v>910</v>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>0:09:50</t>
+          <t>0:15:10</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
         <v>4</v>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>면취</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>2</v>
       </c>
       <c r="D21" s="22" t="n">
         <v>10</v>
@@ -1654,36 +1706,40 @@
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>0160 ㅋㅌ</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr"/>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" s="24" t="n">
         <v>2</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>990</v>
+        <v>546</v>
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>0:16:30</t>
+          <t>0:09:06</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>드릴</t>
+          <t>R0.3_라핑</t>
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="E22" s="22" t="n">
         <v>10</v>
@@ -1695,53 +1751,282 @@
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
+          <t>0160</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="24" t="n">
+        <v>590</v>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>0:09:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>0160 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="24" t="n">
+        <v>990</v>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>0:16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
           <t>0149</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr"/>
-      <c r="I22" s="24" t="n">
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="J22" s="24" t="n">
+      <c r="J24" s="24" t="n">
         <v>4301</v>
       </c>
-      <c r="K22" s="22" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>1:11:41</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>0120, 0149</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" s="24" t="n">
+        <v>972</v>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>0:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>0120, 0149</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="24" t="n">
+        <v>486</v>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>0:08:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>틴</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>0175</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>0:04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>7337</v>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>2:02:17</t>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>9035</v>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>2:30:35</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/wiki/reports/daily/2026-10-08_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-08_일일보고.xlsx
@@ -613,7 +613,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-08 16:53   |   전일: 10월 7일   |   월평균 기준: 이전 작업일 4일 평균   |   10월 누적 작업일: 5일</t>
+          <t>생성: 2026-10-08 16:55   |   전일: 10월 7일   |   월평균 기준: 이전 작업일 4일 평균   |   10월 누적 작업일: 5일</t>
         </is>
       </c>
     </row>
